--- a/2026_3ds_sched.xlsx
+++ b/2026_3ds_sched.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dacdatalabs.ojt7\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dacdatalabs.ojt7\de_works\Mall Branch Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63B975B4-0158-4298-AC35-82BFD66EDEA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F0490B-35B8-4312-B779-8D6D932A87BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$744</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$752</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2978" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3010" uniqueCount="118">
   <si>
     <t>branch_name</t>
   </si>
@@ -374,6 +374,9 @@
   </si>
   <si>
     <t>4ds</t>
+  </si>
+  <si>
+    <t>Laoag</t>
   </si>
 </sst>
 </file>
@@ -735,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F744"/>
+  <dimension ref="A1:F752"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.54296875" customWidth="1"/>
@@ -7148,7 +7151,7 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="B321">
         <v>2026</v>
@@ -7168,7 +7171,7 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="B322">
         <v>2026</v>
@@ -7188,7 +7191,7 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="B323">
         <v>2026</v>
@@ -7208,7 +7211,7 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="B324">
         <v>2026</v>
@@ -7228,7 +7231,7 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B325">
         <v>2026</v>
@@ -7237,18 +7240,18 @@
         <v>7</v>
       </c>
       <c r="D325" s="1">
-        <v>46169</v>
+        <v>46156</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
       </c>
       <c r="F325" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B326">
         <v>2026</v>
@@ -7257,18 +7260,18 @@
         <v>7</v>
       </c>
       <c r="D326" s="1">
-        <v>46170</v>
+        <v>46157</v>
       </c>
       <c r="E326" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F326" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B327">
         <v>2026</v>
@@ -7277,18 +7280,18 @@
         <v>7</v>
       </c>
       <c r="D327" s="1">
-        <v>46171</v>
+        <v>46158</v>
       </c>
       <c r="E327" t="s">
         <v>9</v>
       </c>
       <c r="F327" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B328">
         <v>2026</v>
@@ -7297,13 +7300,13 @@
         <v>7</v>
       </c>
       <c r="D328" s="1">
-        <v>46172</v>
+        <v>46159</v>
       </c>
       <c r="E328" t="s">
         <v>9</v>
       </c>
       <c r="F328" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.35">
@@ -7317,10 +7320,10 @@
         <v>7</v>
       </c>
       <c r="D329" s="1">
-        <v>46173</v>
+        <v>46169</v>
       </c>
       <c r="E329" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F329" t="s">
         <v>114</v>
@@ -7328,7 +7331,7 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B330">
         <v>2026</v>
@@ -7343,12 +7346,12 @@
         <v>8</v>
       </c>
       <c r="F330" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B331">
         <v>2026</v>
@@ -7363,12 +7366,12 @@
         <v>9</v>
       </c>
       <c r="F331" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B332">
         <v>2026</v>
@@ -7383,12 +7386,12 @@
         <v>9</v>
       </c>
       <c r="F332" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B333">
         <v>2026</v>
@@ -7403,12 +7406,12 @@
         <v>9</v>
       </c>
       <c r="F333" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B334">
         <v>2026</v>
@@ -7428,7 +7431,7 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B335">
         <v>2026</v>
@@ -7448,7 +7451,7 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B336">
         <v>2026</v>
@@ -7468,7 +7471,7 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B337">
         <v>2026</v>
@@ -7488,7 +7491,7 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B338">
         <v>2026</v>
@@ -7508,7 +7511,7 @@
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B339">
         <v>2026</v>
@@ -7528,7 +7531,7 @@
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B340">
         <v>2026</v>
@@ -7548,7 +7551,7 @@
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B341">
         <v>2026</v>
@@ -7568,7 +7571,7 @@
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B342">
         <v>2026</v>
@@ -7588,7 +7591,7 @@
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B343">
         <v>2026</v>
@@ -7608,7 +7611,7 @@
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B344">
         <v>2026</v>
@@ -7628,7 +7631,7 @@
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B345">
         <v>2026</v>
@@ -7648,7 +7651,7 @@
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B346">
         <v>2026</v>
@@ -7668,7 +7671,7 @@
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B347">
         <v>2026</v>
@@ -7688,7 +7691,7 @@
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B348">
         <v>2026</v>
@@ -7708,7 +7711,7 @@
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B349">
         <v>2026</v>
@@ -7728,7 +7731,7 @@
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B350">
         <v>2026</v>
@@ -7748,7 +7751,7 @@
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B351">
         <v>2026</v>
@@ -7768,7 +7771,7 @@
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B352">
         <v>2026</v>
@@ -7788,7 +7791,7 @@
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B353">
         <v>2026</v>
@@ -7808,7 +7811,7 @@
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B354">
         <v>2026</v>
@@ -7828,7 +7831,7 @@
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B355">
         <v>2026</v>
@@ -7848,7 +7851,7 @@
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B356">
         <v>2026</v>
@@ -7868,7 +7871,7 @@
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B357">
         <v>2026</v>
@@ -7888,7 +7891,7 @@
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B358">
         <v>2026</v>
@@ -7908,7 +7911,7 @@
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B359">
         <v>2026</v>
@@ -7928,7 +7931,7 @@
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B360">
         <v>2026</v>
@@ -7948,7 +7951,7 @@
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B361">
         <v>2026</v>
@@ -7968,7 +7971,7 @@
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B362">
         <v>2026</v>
@@ -7977,7 +7980,7 @@
         <v>7</v>
       </c>
       <c r="D362" s="1">
-        <v>46184</v>
+        <v>46170</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -7988,7 +7991,7 @@
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B363">
         <v>2026</v>
@@ -7997,7 +8000,7 @@
         <v>7</v>
       </c>
       <c r="D363" s="1">
-        <v>46185</v>
+        <v>46171</v>
       </c>
       <c r="E363" t="s">
         <v>9</v>
@@ -8008,7 +8011,7 @@
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B364">
         <v>2026</v>
@@ -8017,7 +8020,7 @@
         <v>7</v>
       </c>
       <c r="D364" s="1">
-        <v>46186</v>
+        <v>46172</v>
       </c>
       <c r="E364" t="s">
         <v>9</v>
@@ -8028,7 +8031,7 @@
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B365">
         <v>2026</v>
@@ -8037,7 +8040,7 @@
         <v>7</v>
       </c>
       <c r="D365" s="1">
-        <v>46187</v>
+        <v>46173</v>
       </c>
       <c r="E365" t="s">
         <v>9</v>
@@ -8048,7 +8051,7 @@
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B366">
         <v>2026</v>
@@ -8068,7 +8071,7 @@
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B367">
         <v>2026</v>
@@ -8088,7 +8091,7 @@
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B368">
         <v>2026</v>
@@ -8108,7 +8111,7 @@
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B369">
         <v>2026</v>
@@ -8128,7 +8131,7 @@
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B370">
         <v>2026</v>
@@ -8148,7 +8151,7 @@
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B371">
         <v>2026</v>
@@ -8168,7 +8171,7 @@
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B372">
         <v>2026</v>
@@ -8188,7 +8191,7 @@
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B373">
         <v>2026</v>
@@ -8208,82 +8211,82 @@
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>6</v>
+        <v>92</v>
       </c>
       <c r="B374">
         <v>2026</v>
       </c>
       <c r="C374" t="s">
-        <v>93</v>
+        <v>7</v>
       </c>
       <c r="D374" s="1">
-        <v>46218</v>
+        <v>46184</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
       </c>
       <c r="F374" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>6</v>
+        <v>92</v>
       </c>
       <c r="B375">
         <v>2026</v>
       </c>
       <c r="C375" t="s">
-        <v>93</v>
+        <v>7</v>
       </c>
       <c r="D375" s="1">
-        <v>46219</v>
+        <v>46185</v>
       </c>
       <c r="E375" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F375" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>6</v>
+        <v>92</v>
       </c>
       <c r="B376">
         <v>2026</v>
       </c>
       <c r="C376" t="s">
-        <v>93</v>
+        <v>7</v>
       </c>
       <c r="D376" s="1">
-        <v>46220</v>
+        <v>46186</v>
       </c>
       <c r="E376" t="s">
         <v>9</v>
       </c>
       <c r="F376" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>6</v>
+        <v>92</v>
       </c>
       <c r="B377">
         <v>2026</v>
       </c>
       <c r="C377" t="s">
-        <v>93</v>
+        <v>7</v>
       </c>
       <c r="D377" s="1">
-        <v>46221</v>
+        <v>46187</v>
       </c>
       <c r="E377" t="s">
         <v>9</v>
       </c>
       <c r="F377" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.35">
@@ -8297,10 +8300,10 @@
         <v>93</v>
       </c>
       <c r="D378" s="1">
-        <v>46222</v>
+        <v>46218</v>
       </c>
       <c r="E378" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F378" t="s">
         <v>114</v>
@@ -8308,7 +8311,7 @@
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B379">
         <v>2026</v>
@@ -8323,12 +8326,12 @@
         <v>8</v>
       </c>
       <c r="F379" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B380">
         <v>2026</v>
@@ -8343,12 +8346,12 @@
         <v>9</v>
       </c>
       <c r="F380" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B381">
         <v>2026</v>
@@ -8363,12 +8366,12 @@
         <v>9</v>
       </c>
       <c r="F381" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B382">
         <v>2026</v>
@@ -8383,12 +8386,12 @@
         <v>9</v>
       </c>
       <c r="F382" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B383">
         <v>2026</v>
@@ -8408,7 +8411,7 @@
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B384">
         <v>2026</v>
@@ -8428,7 +8431,7 @@
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B385">
         <v>2026</v>
@@ -8448,7 +8451,7 @@
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B386">
         <v>2026</v>
@@ -8468,7 +8471,7 @@
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B387">
         <v>2026</v>
@@ -8488,7 +8491,7 @@
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B388">
         <v>2026</v>
@@ -8508,7 +8511,7 @@
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B389">
         <v>2026</v>
@@ -8528,7 +8531,7 @@
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B390">
         <v>2026</v>
@@ -8548,7 +8551,7 @@
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B391">
         <v>2026</v>
@@ -8568,7 +8571,7 @@
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B392">
         <v>2026</v>
@@ -8588,7 +8591,7 @@
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B393">
         <v>2026</v>
@@ -8608,7 +8611,7 @@
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B394">
         <v>2026</v>
@@ -8628,7 +8631,7 @@
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B395">
         <v>2026</v>
@@ -8648,7 +8651,7 @@
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B396">
         <v>2026</v>
@@ -8668,7 +8671,7 @@
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B397">
         <v>2026</v>
@@ -8688,7 +8691,7 @@
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B398">
         <v>2026</v>
@@ -8708,7 +8711,7 @@
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B399">
         <v>2026</v>
@@ -8717,10 +8720,10 @@
         <v>93</v>
       </c>
       <c r="D399" s="1">
-        <v>46234</v>
+        <v>46219</v>
       </c>
       <c r="E399" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F399" t="s">
         <v>115</v>
@@ -8728,7 +8731,7 @@
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B400">
         <v>2026</v>
@@ -8737,7 +8740,7 @@
         <v>93</v>
       </c>
       <c r="D400" s="1">
-        <v>46235</v>
+        <v>46220</v>
       </c>
       <c r="E400" t="s">
         <v>9</v>
@@ -8748,7 +8751,7 @@
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B401">
         <v>2026</v>
@@ -8757,7 +8760,7 @@
         <v>93</v>
       </c>
       <c r="D401" s="1">
-        <v>46236</v>
+        <v>46221</v>
       </c>
       <c r="E401" t="s">
         <v>9</v>
@@ -8768,7 +8771,7 @@
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B402">
         <v>2026</v>
@@ -8777,10 +8780,10 @@
         <v>93</v>
       </c>
       <c r="D402" s="1">
-        <v>46233</v>
+        <v>46222</v>
       </c>
       <c r="E402" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F402" t="s">
         <v>115</v>
@@ -8788,7 +8791,7 @@
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B403">
         <v>2026</v>
@@ -8797,7 +8800,7 @@
         <v>93</v>
       </c>
       <c r="D403" s="1">
-        <v>46235</v>
+        <v>46234</v>
       </c>
       <c r="E403" t="s">
         <v>9</v>
@@ -8808,7 +8811,7 @@
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B404">
         <v>2026</v>
@@ -8817,7 +8820,7 @@
         <v>93</v>
       </c>
       <c r="D404" s="1">
-        <v>46236</v>
+        <v>46235</v>
       </c>
       <c r="E404" t="s">
         <v>9</v>
@@ -8828,7 +8831,7 @@
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B405">
         <v>2026</v>
@@ -8837,7 +8840,7 @@
         <v>93</v>
       </c>
       <c r="D405" s="1">
-        <v>46237</v>
+        <v>46236</v>
       </c>
       <c r="E405" t="s">
         <v>9</v>
@@ -8848,7 +8851,7 @@
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B406">
         <v>2026</v>
@@ -8868,7 +8871,7 @@
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B407">
         <v>2026</v>
@@ -8888,7 +8891,7 @@
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B408">
         <v>2026</v>
@@ -8908,7 +8911,7 @@
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B409">
         <v>2026</v>
@@ -8928,7 +8931,7 @@
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B410">
         <v>2026</v>
@@ -8948,7 +8951,7 @@
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B411">
         <v>2026</v>
@@ -8968,7 +8971,7 @@
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B412">
         <v>2026</v>
@@ -8988,7 +8991,7 @@
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B413">
         <v>2026</v>
@@ -9008,7 +9011,7 @@
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B414">
         <v>2026</v>
@@ -9028,7 +9031,7 @@
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B415">
         <v>2026</v>
@@ -9048,7 +9051,7 @@
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B416">
         <v>2026</v>
@@ -9068,7 +9071,7 @@
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B417">
         <v>2026</v>
@@ -9088,7 +9091,7 @@
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B418">
         <v>2026</v>
@@ -9108,7 +9111,7 @@
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B419">
         <v>2026</v>
@@ -9128,7 +9131,7 @@
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B420">
         <v>2026</v>
@@ -9148,7 +9151,7 @@
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B421">
         <v>2026</v>
@@ -9168,7 +9171,7 @@
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B422">
         <v>2026</v>
@@ -9188,7 +9191,7 @@
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B423">
         <v>2026</v>
@@ -9208,7 +9211,7 @@
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B424">
         <v>2026</v>
@@ -9228,7 +9231,7 @@
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B425">
         <v>2026</v>
@@ -9248,7 +9251,7 @@
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B426">
         <v>2026</v>
@@ -9268,7 +9271,7 @@
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B427">
         <v>2026</v>
@@ -9288,7 +9291,7 @@
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B428">
         <v>2026</v>
@@ -9308,7 +9311,7 @@
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B429">
         <v>2026</v>
@@ -9328,7 +9331,7 @@
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="B430">
         <v>2026</v>
@@ -9348,7 +9351,7 @@
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="B431">
         <v>2026</v>
@@ -9368,7 +9371,7 @@
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="B432">
         <v>2026</v>
@@ -9388,7 +9391,7 @@
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="B433">
         <v>2026</v>
@@ -9408,7 +9411,7 @@
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="B434">
         <v>2026</v>
@@ -9428,7 +9431,7 @@
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="B435">
         <v>2026</v>
@@ -9448,7 +9451,7 @@
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="B436">
         <v>2026</v>
@@ -9468,7 +9471,7 @@
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="B437">
         <v>2026</v>
@@ -9488,7 +9491,7 @@
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="B438">
         <v>2026</v>
@@ -9497,7 +9500,7 @@
         <v>93</v>
       </c>
       <c r="D438" s="1">
-        <v>46247</v>
+        <v>46233</v>
       </c>
       <c r="E438" t="s">
         <v>8</v>
@@ -9508,7 +9511,7 @@
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="B439">
         <v>2026</v>
@@ -9517,7 +9520,7 @@
         <v>93</v>
       </c>
       <c r="D439" s="1">
-        <v>46248</v>
+        <v>46235</v>
       </c>
       <c r="E439" t="s">
         <v>9</v>
@@ -9528,7 +9531,7 @@
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="B440">
         <v>2026</v>
@@ -9537,7 +9540,7 @@
         <v>93</v>
       </c>
       <c r="D440" s="1">
-        <v>46249</v>
+        <v>46236</v>
       </c>
       <c r="E440" t="s">
         <v>9</v>
@@ -9548,7 +9551,7 @@
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="B441">
         <v>2026</v>
@@ -9557,7 +9560,7 @@
         <v>93</v>
       </c>
       <c r="D441" s="1">
-        <v>46250</v>
+        <v>46237</v>
       </c>
       <c r="E441" t="s">
         <v>9</v>
@@ -9568,7 +9571,7 @@
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="B442">
         <v>2026</v>
@@ -9588,7 +9591,7 @@
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="B443">
         <v>2026</v>
@@ -9608,7 +9611,7 @@
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="B444">
         <v>2026</v>
@@ -9628,7 +9631,7 @@
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="B445">
         <v>2026</v>
@@ -9648,7 +9651,7 @@
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B446">
         <v>2026</v>
@@ -9668,7 +9671,7 @@
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B447">
         <v>2026</v>
@@ -9688,7 +9691,7 @@
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B448">
         <v>2026</v>
@@ -9708,7 +9711,7 @@
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B449">
         <v>2026</v>
@@ -9728,7 +9731,7 @@
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B450">
         <v>2026</v>
@@ -9748,7 +9751,7 @@
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B451">
         <v>2026</v>
@@ -9768,7 +9771,7 @@
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B452">
         <v>2026</v>
@@ -9788,7 +9791,7 @@
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B453">
         <v>2026</v>
@@ -9808,7 +9811,7 @@
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B454">
         <v>2026</v>
@@ -9828,7 +9831,7 @@
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B455">
         <v>2026</v>
@@ -9848,7 +9851,7 @@
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B456">
         <v>2026</v>
@@ -9868,7 +9871,7 @@
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B457">
         <v>2026</v>
@@ -9888,7 +9891,7 @@
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B458">
         <v>2026</v>
@@ -9908,7 +9911,7 @@
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B459">
         <v>2026</v>
@@ -9928,7 +9931,7 @@
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B460">
         <v>2026</v>
@@ -9948,7 +9951,7 @@
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B461">
         <v>2026</v>
@@ -9968,7 +9971,7 @@
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B462">
         <v>2026</v>
@@ -9988,7 +9991,7 @@
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B463">
         <v>2026</v>
@@ -10008,7 +10011,7 @@
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B464">
         <v>2026</v>
@@ -10028,7 +10031,7 @@
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B465">
         <v>2026</v>
@@ -10048,7 +10051,7 @@
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B466">
         <v>2026</v>
@@ -10068,7 +10071,7 @@
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B467">
         <v>2026</v>
@@ -10088,7 +10091,7 @@
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B468">
         <v>2026</v>
@@ -10108,7 +10111,7 @@
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B469">
         <v>2026</v>
@@ -10128,7 +10131,7 @@
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="B470">
         <v>2026</v>
@@ -10137,10 +10140,10 @@
         <v>93</v>
       </c>
       <c r="D470" s="1">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="E470" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F470" t="s">
         <v>115</v>
@@ -10148,7 +10151,7 @@
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="B471">
         <v>2026</v>
@@ -10157,7 +10160,7 @@
         <v>93</v>
       </c>
       <c r="D471" s="1">
-        <v>46249</v>
+        <v>46248</v>
       </c>
       <c r="E471" t="s">
         <v>9</v>
@@ -10168,7 +10171,7 @@
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="B472">
         <v>2026</v>
@@ -10177,7 +10180,7 @@
         <v>93</v>
       </c>
       <c r="D472" s="1">
-        <v>46250</v>
+        <v>46249</v>
       </c>
       <c r="E472" t="s">
         <v>9</v>
@@ -10188,7 +10191,7 @@
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B473">
         <v>2026</v>
@@ -10197,10 +10200,10 @@
         <v>93</v>
       </c>
       <c r="D473" s="1">
-        <v>46247</v>
+        <v>46250</v>
       </c>
       <c r="E473" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F473" t="s">
         <v>115</v>
@@ -10208,7 +10211,7 @@
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
       <c r="B474">
         <v>2026</v>
@@ -10228,7 +10231,7 @@
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
       <c r="B475">
         <v>2026</v>
@@ -10248,7 +10251,7 @@
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
       <c r="B476">
         <v>2026</v>
@@ -10268,7 +10271,7 @@
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="B477">
         <v>2026</v>
@@ -10288,7 +10291,7 @@
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="B478">
         <v>2026</v>
@@ -10308,7 +10311,7 @@
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="B479">
         <v>2026</v>
@@ -10328,7 +10331,7 @@
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="B480">
         <v>2026</v>
@@ -10348,7 +10351,7 @@
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="B481">
         <v>2026</v>
@@ -10368,7 +10371,7 @@
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="B482">
         <v>2026</v>
@@ -10388,7 +10391,7 @@
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="B483">
         <v>2026</v>
@@ -10408,7 +10411,7 @@
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="B484">
         <v>2026</v>
@@ -10428,7 +10431,7 @@
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="B485">
         <v>2026</v>
@@ -10437,10 +10440,10 @@
         <v>93</v>
       </c>
       <c r="D485" s="1">
-        <v>46255</v>
+        <v>46247</v>
       </c>
       <c r="E485" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F485" t="s">
         <v>115</v>
@@ -10448,7 +10451,7 @@
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="B486">
         <v>2026</v>
@@ -10457,7 +10460,7 @@
         <v>93</v>
       </c>
       <c r="D486" s="1">
-        <v>46256</v>
+        <v>46248</v>
       </c>
       <c r="E486" t="s">
         <v>9</v>
@@ -10468,7 +10471,7 @@
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="B487">
         <v>2026</v>
@@ -10477,7 +10480,7 @@
         <v>93</v>
       </c>
       <c r="D487" s="1">
-        <v>46257</v>
+        <v>46249</v>
       </c>
       <c r="E487" t="s">
         <v>9</v>
@@ -10488,7 +10491,7 @@
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B488">
         <v>2026</v>
@@ -10497,10 +10500,10 @@
         <v>93</v>
       </c>
       <c r="D488" s="1">
-        <v>46261</v>
+        <v>46250</v>
       </c>
       <c r="E488" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F488" t="s">
         <v>115</v>
@@ -10508,7 +10511,7 @@
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="B489">
         <v>2026</v>
@@ -10517,7 +10520,7 @@
         <v>93</v>
       </c>
       <c r="D489" s="1">
-        <v>46262</v>
+        <v>46255</v>
       </c>
       <c r="E489" t="s">
         <v>9</v>
@@ -10528,7 +10531,7 @@
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="B490">
         <v>2026</v>
@@ -10537,7 +10540,7 @@
         <v>93</v>
       </c>
       <c r="D490" s="1">
-        <v>46263</v>
+        <v>46256</v>
       </c>
       <c r="E490" t="s">
         <v>9</v>
@@ -10548,7 +10551,7 @@
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="B491">
         <v>2026</v>
@@ -10557,7 +10560,7 @@
         <v>93</v>
       </c>
       <c r="D491" s="1">
-        <v>46264</v>
+        <v>46257</v>
       </c>
       <c r="E491" t="s">
         <v>9</v>
@@ -10568,7 +10571,7 @@
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="B492">
         <v>2026</v>
@@ -10588,7 +10591,7 @@
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="B493">
         <v>2026</v>
@@ -10608,7 +10611,7 @@
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="B494">
         <v>2026</v>
@@ -10628,7 +10631,7 @@
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="B495">
         <v>2026</v>
@@ -10648,7 +10651,7 @@
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="B496">
         <v>2026</v>
@@ -10668,7 +10671,7 @@
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="B497">
         <v>2026</v>
@@ -10688,7 +10691,7 @@
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="B498">
         <v>2026</v>
@@ -10708,7 +10711,7 @@
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="B499">
         <v>2026</v>
@@ -10728,7 +10731,7 @@
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="B500">
         <v>2026</v>
@@ -10748,7 +10751,7 @@
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="B501">
         <v>2026</v>
@@ -10768,7 +10771,7 @@
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="B502">
         <v>2026</v>
@@ -10788,7 +10791,7 @@
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="B503">
         <v>2026</v>
@@ -10808,7 +10811,7 @@
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B504">
         <v>2026</v>
@@ -10828,7 +10831,7 @@
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B505">
         <v>2026</v>
@@ -10848,7 +10851,7 @@
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B506">
         <v>2026</v>
@@ -10868,7 +10871,7 @@
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B507">
         <v>2026</v>
@@ -10888,7 +10891,7 @@
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B508">
         <v>2026</v>
@@ -10908,7 +10911,7 @@
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B509">
         <v>2026</v>
@@ -10928,7 +10931,7 @@
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B510">
         <v>2026</v>
@@ -10948,7 +10951,7 @@
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B511">
         <v>2026</v>
@@ -10968,7 +10971,7 @@
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="B512">
         <v>2026</v>
@@ -10988,7 +10991,7 @@
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="B513">
         <v>2026</v>
@@ -11008,7 +11011,7 @@
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="B514">
         <v>2026</v>
@@ -11028,7 +11031,7 @@
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="B515">
         <v>2026</v>
@@ -11048,7 +11051,7 @@
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="B516">
         <v>2026</v>
@@ -11068,7 +11071,7 @@
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="B517">
         <v>2026</v>
@@ -11088,7 +11091,7 @@
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="B518">
         <v>2026</v>
@@ -11108,7 +11111,7 @@
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="B519">
         <v>2026</v>
@@ -11128,7 +11131,7 @@
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="B520">
         <v>2026</v>
@@ -11148,7 +11151,7 @@
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="B521">
         <v>2026</v>
@@ -11168,7 +11171,7 @@
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="B522">
         <v>2026</v>
@@ -11188,7 +11191,7 @@
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="B523">
         <v>2026</v>
@@ -11208,7 +11211,7 @@
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B524">
         <v>2026</v>
@@ -11228,7 +11231,7 @@
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B525">
         <v>2026</v>
@@ -11248,7 +11251,7 @@
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B526">
         <v>2026</v>
@@ -11268,7 +11271,7 @@
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B527">
         <v>2026</v>
@@ -11288,7 +11291,7 @@
     </row>
     <row r="528" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B528">
         <v>2026</v>
@@ -11308,7 +11311,7 @@
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B529">
         <v>2026</v>
@@ -11328,7 +11331,7 @@
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B530">
         <v>2026</v>
@@ -11348,7 +11351,7 @@
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B531">
         <v>2026</v>
@@ -11368,7 +11371,7 @@
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="B532">
         <v>2026</v>
@@ -11377,10 +11380,10 @@
         <v>93</v>
       </c>
       <c r="D532" s="1">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="E532" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F532" t="s">
         <v>115</v>
@@ -11388,7 +11391,7 @@
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="B533">
         <v>2026</v>
@@ -11397,7 +11400,7 @@
         <v>93</v>
       </c>
       <c r="D533" s="1">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="E533" t="s">
         <v>9</v>
@@ -11408,7 +11411,7 @@
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="B534">
         <v>2026</v>
@@ -11417,7 +11420,7 @@
         <v>93</v>
       </c>
       <c r="D534" s="1">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="E534" t="s">
         <v>9</v>
@@ -11428,7 +11431,7 @@
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="B535">
         <v>2026</v>
@@ -11437,7 +11440,7 @@
         <v>93</v>
       </c>
       <c r="D535" s="1">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="E535" t="s">
         <v>9</v>
@@ -11448,7 +11451,7 @@
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B536">
         <v>2026</v>
@@ -11457,7 +11460,7 @@
         <v>93</v>
       </c>
       <c r="D536" s="1">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="E536" t="s">
         <v>9</v>
@@ -11468,7 +11471,7 @@
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B537">
         <v>2026</v>
@@ -11477,7 +11480,7 @@
         <v>93</v>
       </c>
       <c r="D537" s="1">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="E537" t="s">
         <v>9</v>
@@ -11488,7 +11491,7 @@
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B538">
         <v>2026</v>
@@ -11497,7 +11500,7 @@
         <v>93</v>
       </c>
       <c r="D538" s="1">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="E538" t="s">
         <v>9</v>
@@ -11508,7 +11511,7 @@
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B539">
         <v>2026</v>
@@ -11517,7 +11520,7 @@
         <v>93</v>
       </c>
       <c r="D539" s="1">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="E539" t="s">
         <v>9</v>
@@ -11528,7 +11531,7 @@
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B540">
         <v>2026</v>
@@ -11537,7 +11540,7 @@
         <v>93</v>
       </c>
       <c r="D540" s="1">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="E540" t="s">
         <v>9</v>
@@ -11548,7 +11551,7 @@
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B541">
         <v>2026</v>
@@ -11557,7 +11560,7 @@
         <v>93</v>
       </c>
       <c r="D541" s="1">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="E541" t="s">
         <v>9</v>
@@ -11568,7 +11571,7 @@
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B542">
         <v>2026</v>
@@ -11577,7 +11580,7 @@
         <v>93</v>
       </c>
       <c r="D542" s="1">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="E542" t="s">
         <v>9</v>
@@ -11588,7 +11591,7 @@
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B543">
         <v>2026</v>
@@ -11597,7 +11600,7 @@
         <v>93</v>
       </c>
       <c r="D543" s="1">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="E543" t="s">
         <v>9</v>
@@ -11608,7 +11611,7 @@
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="B544">
         <v>2026</v>
@@ -11617,18 +11620,18 @@
         <v>93</v>
       </c>
       <c r="D544" s="1">
-        <v>46281</v>
+        <v>46264</v>
       </c>
       <c r="E544" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F544" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="B545">
         <v>2026</v>
@@ -11637,18 +11640,18 @@
         <v>93</v>
       </c>
       <c r="D545" s="1">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="E545" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F545" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="B546">
         <v>2026</v>
@@ -11657,18 +11660,18 @@
         <v>93</v>
       </c>
       <c r="D546" s="1">
-        <v>46283</v>
+        <v>46263</v>
       </c>
       <c r="E546" t="s">
         <v>9</v>
       </c>
       <c r="F546" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="B547">
         <v>2026</v>
@@ -11677,13 +11680,13 @@
         <v>93</v>
       </c>
       <c r="D547" s="1">
-        <v>46284</v>
+        <v>46264</v>
       </c>
       <c r="E547" t="s">
         <v>9</v>
       </c>
       <c r="F547" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.35">
@@ -11697,10 +11700,10 @@
         <v>93</v>
       </c>
       <c r="D548" s="1">
-        <v>46285</v>
+        <v>46281</v>
       </c>
       <c r="E548" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F548" t="s">
         <v>114</v>
@@ -11708,7 +11711,7 @@
     </row>
     <row r="549" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B549">
         <v>2026</v>
@@ -11717,7 +11720,7 @@
         <v>93</v>
       </c>
       <c r="D549" s="1">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E549" t="s">
         <v>8</v>
@@ -11728,7 +11731,7 @@
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B550">
         <v>2026</v>
@@ -11737,10 +11740,10 @@
         <v>93</v>
       </c>
       <c r="D550" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E550" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F550" t="s">
         <v>114</v>
@@ -11748,7 +11751,7 @@
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B551">
         <v>2026</v>
@@ -11757,7 +11760,7 @@
         <v>93</v>
       </c>
       <c r="D551" s="1">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E551" t="s">
         <v>9</v>
@@ -11768,7 +11771,7 @@
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B552">
         <v>2026</v>
@@ -11777,7 +11780,7 @@
         <v>93</v>
       </c>
       <c r="D552" s="1">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E552" t="s">
         <v>9</v>
@@ -11797,10 +11800,10 @@
         <v>93</v>
       </c>
       <c r="D553" s="1">
-        <v>46285</v>
+        <v>46281</v>
       </c>
       <c r="E553" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F553" t="s">
         <v>114</v>
@@ -11808,7 +11811,7 @@
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B554">
         <v>2026</v>
@@ -11817,7 +11820,7 @@
         <v>93</v>
       </c>
       <c r="D554" s="1">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E554" t="s">
         <v>8</v>
@@ -11828,7 +11831,7 @@
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B555">
         <v>2026</v>
@@ -11837,10 +11840,10 @@
         <v>93</v>
       </c>
       <c r="D555" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E555" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F555" t="s">
         <v>114</v>
@@ -11848,7 +11851,7 @@
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B556">
         <v>2026</v>
@@ -11857,7 +11860,7 @@
         <v>93</v>
       </c>
       <c r="D556" s="1">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E556" t="s">
         <v>9</v>
@@ -11868,7 +11871,7 @@
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B557">
         <v>2026</v>
@@ -11877,7 +11880,7 @@
         <v>93</v>
       </c>
       <c r="D557" s="1">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E557" t="s">
         <v>9</v>
@@ -11897,10 +11900,10 @@
         <v>93</v>
       </c>
       <c r="D558" s="1">
-        <v>46285</v>
+        <v>46281</v>
       </c>
       <c r="E558" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F558" t="s">
         <v>114</v>
@@ -11908,7 +11911,7 @@
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B559">
         <v>2026</v>
@@ -11923,12 +11926,12 @@
         <v>8</v>
       </c>
       <c r="F559" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B560">
         <v>2026</v>
@@ -11943,12 +11946,12 @@
         <v>9</v>
       </c>
       <c r="F560" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B561">
         <v>2026</v>
@@ -11963,12 +11966,12 @@
         <v>9</v>
       </c>
       <c r="F561" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B562">
         <v>2026</v>
@@ -11983,12 +11986,12 @@
         <v>9</v>
       </c>
       <c r="F562" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="B563">
         <v>2026</v>
@@ -12008,7 +12011,7 @@
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="B564">
         <v>2026</v>
@@ -12028,7 +12031,7 @@
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="B565">
         <v>2026</v>
@@ -12048,7 +12051,7 @@
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="B566">
         <v>2026</v>
@@ -12068,7 +12071,7 @@
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="B567">
         <v>2026</v>
@@ -12088,7 +12091,7 @@
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="B568">
         <v>2026</v>
@@ -12108,7 +12111,7 @@
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="B569">
         <v>2026</v>
@@ -12128,7 +12131,7 @@
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="B570">
         <v>2026</v>
@@ -12148,7 +12151,7 @@
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="B571">
         <v>2026</v>
@@ -12168,7 +12171,7 @@
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="B572">
         <v>2026</v>
@@ -12188,7 +12191,7 @@
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="B573">
         <v>2026</v>
@@ -12208,7 +12211,7 @@
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="B574">
         <v>2026</v>
@@ -12228,7 +12231,7 @@
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="B575">
         <v>2026</v>
@@ -12248,7 +12251,7 @@
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="B576">
         <v>2026</v>
@@ -12268,7 +12271,7 @@
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="B577">
         <v>2026</v>
@@ -12288,7 +12291,7 @@
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="B578">
         <v>2026</v>
@@ -12308,7 +12311,7 @@
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="B579">
         <v>2026</v>
@@ -12328,7 +12331,7 @@
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="B580">
         <v>2026</v>
@@ -12348,7 +12351,7 @@
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="B581">
         <v>2026</v>
@@ -12368,7 +12371,7 @@
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="B582">
         <v>2026</v>
@@ -12388,7 +12391,7 @@
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B583">
         <v>2026</v>
@@ -12408,7 +12411,7 @@
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B584">
         <v>2026</v>
@@ -12428,7 +12431,7 @@
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B585">
         <v>2026</v>
@@ -12448,7 +12451,7 @@
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B586">
         <v>2026</v>
@@ -12468,7 +12471,7 @@
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="B587">
         <v>2026</v>
@@ -12488,7 +12491,7 @@
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="B588">
         <v>2026</v>
@@ -12508,7 +12511,7 @@
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="B589">
         <v>2026</v>
@@ -12528,7 +12531,7 @@
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="B590">
         <v>2026</v>
@@ -12548,7 +12551,7 @@
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="B591">
         <v>2026</v>
@@ -12568,7 +12571,7 @@
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="B592">
         <v>2026</v>
@@ -12588,7 +12591,7 @@
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="B593">
         <v>2026</v>
@@ -12608,7 +12611,7 @@
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="B594">
         <v>2026</v>
@@ -12628,7 +12631,7 @@
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="B595">
         <v>2026</v>
@@ -12648,7 +12651,7 @@
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="B596">
         <v>2026</v>
@@ -12668,7 +12671,7 @@
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="B597">
         <v>2026</v>
@@ -12688,7 +12691,7 @@
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="B598">
         <v>2026</v>
@@ -12708,7 +12711,7 @@
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B599">
         <v>2026</v>
@@ -12728,7 +12731,7 @@
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B600">
         <v>2026</v>
@@ -12748,7 +12751,7 @@
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B601">
         <v>2026</v>
@@ -12768,7 +12771,7 @@
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B602">
         <v>2026</v>
@@ -12788,7 +12791,7 @@
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="B603">
         <v>2026</v>
@@ -12808,7 +12811,7 @@
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="B604">
         <v>2026</v>
@@ -12828,7 +12831,7 @@
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="B605">
         <v>2026</v>
@@ -12848,7 +12851,7 @@
     </row>
     <row r="606" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="B606">
         <v>2026</v>
@@ -12868,7 +12871,7 @@
     </row>
     <row r="607" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B607">
         <v>2026</v>
@@ -12888,7 +12891,7 @@
     </row>
     <row r="608" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B608">
         <v>2026</v>
@@ -12908,7 +12911,7 @@
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B609">
         <v>2026</v>
@@ -12928,7 +12931,7 @@
     </row>
     <row r="610" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B610">
         <v>2026</v>
@@ -12948,7 +12951,7 @@
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="B611">
         <v>2026</v>
@@ -12968,7 +12971,7 @@
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="B612">
         <v>2026</v>
@@ -12988,7 +12991,7 @@
     </row>
     <row r="613" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="B613">
         <v>2026</v>
@@ -13008,7 +13011,7 @@
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="B614">
         <v>2026</v>
@@ -13028,7 +13031,7 @@
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B615">
         <v>2026</v>
@@ -13048,7 +13051,7 @@
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B616">
         <v>2026</v>
@@ -13068,7 +13071,7 @@
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B617">
         <v>2026</v>
@@ -13088,7 +13091,7 @@
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B618">
         <v>2026</v>
@@ -13108,7 +13111,7 @@
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="B619">
         <v>2026</v>
@@ -13128,7 +13131,7 @@
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="B620">
         <v>2026</v>
@@ -13148,7 +13151,7 @@
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="B621">
         <v>2026</v>
@@ -13168,7 +13171,7 @@
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="B622">
         <v>2026</v>
@@ -13188,7 +13191,7 @@
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="B623">
         <v>2026</v>
@@ -13197,10 +13200,10 @@
         <v>93</v>
       </c>
       <c r="D623" s="1">
-        <v>46290</v>
+        <v>46282</v>
       </c>
       <c r="E623" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F623" t="s">
         <v>115</v>
@@ -13208,7 +13211,7 @@
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="B624">
         <v>2026</v>
@@ -13217,7 +13220,7 @@
         <v>93</v>
       </c>
       <c r="D624" s="1">
-        <v>46291</v>
+        <v>46283</v>
       </c>
       <c r="E624" t="s">
         <v>9</v>
@@ -13228,7 +13231,7 @@
     </row>
     <row r="625" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="B625">
         <v>2026</v>
@@ -13237,7 +13240,7 @@
         <v>93</v>
       </c>
       <c r="D625" s="1">
-        <v>46292</v>
+        <v>46284</v>
       </c>
       <c r="E625" t="s">
         <v>9</v>
@@ -13248,7 +13251,7 @@
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B626">
         <v>2026</v>
@@ -13257,10 +13260,10 @@
         <v>93</v>
       </c>
       <c r="D626" s="1">
-        <v>46296</v>
+        <v>46285</v>
       </c>
       <c r="E626" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F626" t="s">
         <v>115</v>
@@ -13268,7 +13271,7 @@
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="B627">
         <v>2026</v>
@@ -13277,7 +13280,7 @@
         <v>93</v>
       </c>
       <c r="D627" s="1">
-        <v>46297</v>
+        <v>46290</v>
       </c>
       <c r="E627" t="s">
         <v>9</v>
@@ -13288,7 +13291,7 @@
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="B628">
         <v>2026</v>
@@ -13297,7 +13300,7 @@
         <v>93</v>
       </c>
       <c r="D628" s="1">
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="E628" t="s">
         <v>9</v>
@@ -13308,7 +13311,7 @@
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="B629">
         <v>2026</v>
@@ -13317,7 +13320,7 @@
         <v>93</v>
       </c>
       <c r="D629" s="1">
-        <v>46299</v>
+        <v>46292</v>
       </c>
       <c r="E629" t="s">
         <v>9</v>
@@ -13328,7 +13331,7 @@
     </row>
     <row r="630" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="B630">
         <v>2026</v>
@@ -13348,7 +13351,7 @@
     </row>
     <row r="631" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="B631">
         <v>2026</v>
@@ -13368,7 +13371,7 @@
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="B632">
         <v>2026</v>
@@ -13388,7 +13391,7 @@
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="B633">
         <v>2026</v>
@@ -13408,7 +13411,7 @@
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="B634">
         <v>2026</v>
@@ -13428,7 +13431,7 @@
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="B635">
         <v>2026</v>
@@ -13448,7 +13451,7 @@
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="B636">
         <v>2026</v>
@@ -13468,7 +13471,7 @@
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="B637">
         <v>2026</v>
@@ -13488,7 +13491,7 @@
     </row>
     <row r="638" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B638">
         <v>2026</v>
@@ -13508,7 +13511,7 @@
     </row>
     <row r="639" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B639">
         <v>2026</v>
@@ -13528,7 +13531,7 @@
     </row>
     <row r="640" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B640">
         <v>2026</v>
@@ -13548,7 +13551,7 @@
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B641">
         <v>2026</v>
@@ -13568,7 +13571,7 @@
     </row>
     <row r="642" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B642">
         <v>2026</v>
@@ -13588,7 +13591,7 @@
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B643">
         <v>2026</v>
@@ -13608,7 +13611,7 @@
     </row>
     <row r="644" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B644">
         <v>2026</v>
@@ -13628,7 +13631,7 @@
     </row>
     <row r="645" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B645">
         <v>2026</v>
@@ -13648,7 +13651,7 @@
     </row>
     <row r="646" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B646">
         <v>2026</v>
@@ -13668,7 +13671,7 @@
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B647">
         <v>2026</v>
@@ -13688,7 +13691,7 @@
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B648">
         <v>2026</v>
@@ -13708,7 +13711,7 @@
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B649">
         <v>2026</v>
@@ -13728,7 +13731,7 @@
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B650">
         <v>2026</v>
@@ -13748,7 +13751,7 @@
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B651">
         <v>2026</v>
@@ -13768,7 +13771,7 @@
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B652">
         <v>2026</v>
@@ -13788,7 +13791,7 @@
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B653">
         <v>2026</v>
@@ -13808,7 +13811,7 @@
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="B654">
         <v>2026</v>
@@ -13828,7 +13831,7 @@
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="B655">
         <v>2026</v>
@@ -13848,7 +13851,7 @@
     </row>
     <row r="656" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="B656">
         <v>2026</v>
@@ -13868,7 +13871,7 @@
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="B657">
         <v>2026</v>
@@ -13888,7 +13891,7 @@
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="B658">
         <v>2026</v>
@@ -13897,10 +13900,10 @@
         <v>93</v>
       </c>
       <c r="D658" s="1">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="E658" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F658" t="s">
         <v>115</v>
@@ -13908,7 +13911,7 @@
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="B659">
         <v>2026</v>
@@ -13917,7 +13920,7 @@
         <v>93</v>
       </c>
       <c r="D659" s="1">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="E659" t="s">
         <v>9</v>
@@ -13928,7 +13931,7 @@
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="B660">
         <v>2026</v>
@@ -13937,7 +13940,7 @@
         <v>93</v>
       </c>
       <c r="D660" s="1">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="E660" t="s">
         <v>9</v>
@@ -13948,7 +13951,7 @@
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="B661">
         <v>2026</v>
@@ -13957,7 +13960,7 @@
         <v>93</v>
       </c>
       <c r="D661" s="1">
-        <v>46297</v>
+        <v>46299</v>
       </c>
       <c r="E661" t="s">
         <v>9</v>
@@ -13968,7 +13971,7 @@
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B662">
         <v>2026</v>
@@ -13977,7 +13980,7 @@
         <v>93</v>
       </c>
       <c r="D662" s="1">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="E662" t="s">
         <v>9</v>
@@ -13988,7 +13991,7 @@
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B663">
         <v>2026</v>
@@ -13997,7 +14000,7 @@
         <v>93</v>
       </c>
       <c r="D663" s="1">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="E663" t="s">
         <v>9</v>
@@ -14008,7 +14011,7 @@
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B664">
         <v>2026</v>
@@ -14017,7 +14020,7 @@
         <v>93</v>
       </c>
       <c r="D664" s="1">
-        <v>46297</v>
+        <v>46299</v>
       </c>
       <c r="E664" t="s">
         <v>9</v>
@@ -14028,7 +14031,7 @@
     </row>
     <row r="665" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B665">
         <v>2026</v>
@@ -14037,7 +14040,7 @@
         <v>93</v>
       </c>
       <c r="D665" s="1">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="E665" t="s">
         <v>9</v>
@@ -14048,7 +14051,7 @@
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B666">
         <v>2026</v>
@@ -14057,7 +14060,7 @@
         <v>93</v>
       </c>
       <c r="D666" s="1">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="E666" t="s">
         <v>9</v>
@@ -14068,7 +14071,7 @@
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B667">
         <v>2026</v>
@@ -14077,7 +14080,7 @@
         <v>93</v>
       </c>
       <c r="D667" s="1">
-        <v>46297</v>
+        <v>46299</v>
       </c>
       <c r="E667" t="s">
         <v>9</v>
@@ -14088,7 +14091,7 @@
     </row>
     <row r="668" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B668">
         <v>2026</v>
@@ -14097,7 +14100,7 @@
         <v>93</v>
       </c>
       <c r="D668" s="1">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="E668" t="s">
         <v>9</v>
@@ -14108,7 +14111,7 @@
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B669">
         <v>2026</v>
@@ -14117,7 +14120,7 @@
         <v>93</v>
       </c>
       <c r="D669" s="1">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="E669" t="s">
         <v>9</v>
@@ -14128,7 +14131,7 @@
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="B670">
         <v>2026</v>
@@ -14137,7 +14140,7 @@
         <v>93</v>
       </c>
       <c r="D670" s="1">
-        <v>46312</v>
+        <v>46299</v>
       </c>
       <c r="E670" t="s">
         <v>9</v>
@@ -14148,7 +14151,7 @@
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="B671">
         <v>2026</v>
@@ -14157,7 +14160,7 @@
         <v>93</v>
       </c>
       <c r="D671" s="1">
-        <v>46313</v>
+        <v>46297</v>
       </c>
       <c r="E671" t="s">
         <v>9</v>
@@ -14168,7 +14171,7 @@
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="B672">
         <v>2026</v>
@@ -14177,7 +14180,7 @@
         <v>93</v>
       </c>
       <c r="D672" s="1">
-        <v>46314</v>
+        <v>46298</v>
       </c>
       <c r="E672" t="s">
         <v>9</v>
@@ -14188,7 +14191,7 @@
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="B673">
         <v>2026</v>
@@ -14197,7 +14200,7 @@
         <v>93</v>
       </c>
       <c r="D673" s="1">
-        <v>46314</v>
+        <v>46299</v>
       </c>
       <c r="E673" t="s">
         <v>9</v>
@@ -14208,7 +14211,7 @@
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="B674">
         <v>2026</v>
@@ -14217,10 +14220,10 @@
         <v>93</v>
       </c>
       <c r="D674" s="1">
-        <v>46296</v>
+        <v>46312</v>
       </c>
       <c r="E674" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F674" t="s">
         <v>115</v>
@@ -14228,7 +14231,7 @@
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="B675">
         <v>2026</v>
@@ -14237,7 +14240,7 @@
         <v>93</v>
       </c>
       <c r="D675" s="1">
-        <v>46297</v>
+        <v>46313</v>
       </c>
       <c r="E675" t="s">
         <v>9</v>
@@ -14248,7 +14251,7 @@
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="B676">
         <v>2026</v>
@@ -14257,7 +14260,7 @@
         <v>93</v>
       </c>
       <c r="D676" s="1">
-        <v>46298</v>
+        <v>46314</v>
       </c>
       <c r="E676" t="s">
         <v>9</v>
@@ -14268,7 +14271,7 @@
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="B677">
         <v>2026</v>
@@ -14277,7 +14280,7 @@
         <v>93</v>
       </c>
       <c r="D677" s="1">
-        <v>46299</v>
+        <v>46314</v>
       </c>
       <c r="E677" t="s">
         <v>9</v>
@@ -14288,7 +14291,7 @@
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="B678">
         <v>2026</v>
@@ -14308,7 +14311,7 @@
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="B679">
         <v>2026</v>
@@ -14328,7 +14331,7 @@
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="B680">
         <v>2026</v>
@@ -14348,7 +14351,7 @@
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="B681">
         <v>2026</v>
@@ -14368,7 +14371,7 @@
     </row>
     <row r="682" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="B682">
         <v>2026</v>
@@ -14377,18 +14380,18 @@
         <v>93</v>
       </c>
       <c r="D682" s="1">
-        <v>46309</v>
+        <v>46296</v>
       </c>
       <c r="E682" t="s">
         <v>8</v>
       </c>
       <c r="F682" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="B683">
         <v>2026</v>
@@ -14397,18 +14400,18 @@
         <v>93</v>
       </c>
       <c r="D683" s="1">
-        <v>46310</v>
+        <v>46297</v>
       </c>
       <c r="E683" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F683" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="B684">
         <v>2026</v>
@@ -14417,18 +14420,18 @@
         <v>93</v>
       </c>
       <c r="D684" s="1">
-        <v>46311</v>
+        <v>46298</v>
       </c>
       <c r="E684" t="s">
         <v>9</v>
       </c>
       <c r="F684" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="B685">
         <v>2026</v>
@@ -14437,13 +14440,13 @@
         <v>93</v>
       </c>
       <c r="D685" s="1">
-        <v>46312</v>
+        <v>46299</v>
       </c>
       <c r="E685" t="s">
         <v>9</v>
       </c>
       <c r="F685" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="686" spans="1:6" x14ac:dyDescent="0.35">
@@ -14457,10 +14460,10 @@
         <v>93</v>
       </c>
       <c r="D686" s="1">
-        <v>46313</v>
+        <v>46309</v>
       </c>
       <c r="E686" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F686" t="s">
         <v>114</v>
@@ -14468,7 +14471,7 @@
     </row>
     <row r="687" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B687">
         <v>2026</v>
@@ -14483,12 +14486,12 @@
         <v>8</v>
       </c>
       <c r="F687" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B688">
         <v>2026</v>
@@ -14497,18 +14500,18 @@
         <v>93</v>
       </c>
       <c r="D688" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E688" t="s">
         <v>9</v>
       </c>
       <c r="F688" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="689" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B689">
         <v>2026</v>
@@ -14517,18 +14520,18 @@
         <v>93</v>
       </c>
       <c r="D689" s="1">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E689" t="s">
         <v>9</v>
       </c>
       <c r="F689" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B690">
         <v>2026</v>
@@ -14537,18 +14540,18 @@
         <v>93</v>
       </c>
       <c r="D690" s="1">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E690" t="s">
         <v>9</v>
       </c>
       <c r="F690" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="691" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B691">
         <v>2026</v>
@@ -14568,7 +14571,7 @@
     </row>
     <row r="692" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B692">
         <v>2026</v>
@@ -14577,7 +14580,7 @@
         <v>93</v>
       </c>
       <c r="D692" s="1">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="E692" t="s">
         <v>9</v>
@@ -14588,7 +14591,7 @@
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B693">
         <v>2026</v>
@@ -14597,7 +14600,7 @@
         <v>93</v>
       </c>
       <c r="D693" s="1">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="E693" t="s">
         <v>9</v>
@@ -14608,7 +14611,7 @@
     </row>
     <row r="694" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B694">
         <v>2026</v>
@@ -14617,7 +14620,7 @@
         <v>93</v>
       </c>
       <c r="D694" s="1">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="E694" t="s">
         <v>9</v>
@@ -14628,7 +14631,7 @@
     </row>
     <row r="695" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B695">
         <v>2026</v>
@@ -14648,7 +14651,7 @@
     </row>
     <row r="696" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B696">
         <v>2026</v>
@@ -14668,7 +14671,7 @@
     </row>
     <row r="697" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B697">
         <v>2026</v>
@@ -14688,7 +14691,7 @@
     </row>
     <row r="698" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B698">
         <v>2026</v>
@@ -14708,7 +14711,7 @@
     </row>
     <row r="699" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B699">
         <v>2026</v>
@@ -14728,7 +14731,7 @@
     </row>
     <row r="700" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B700">
         <v>2026</v>
@@ -14748,7 +14751,7 @@
     </row>
     <row r="701" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B701">
         <v>2026</v>
@@ -14768,7 +14771,7 @@
     </row>
     <row r="702" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B702">
         <v>2026</v>
@@ -14788,7 +14791,7 @@
     </row>
     <row r="703" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B703">
         <v>2026</v>
@@ -14808,7 +14811,7 @@
     </row>
     <row r="704" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B704">
         <v>2026</v>
@@ -14828,7 +14831,7 @@
     </row>
     <row r="705" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B705">
         <v>2026</v>
@@ -14848,7 +14851,7 @@
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B706">
         <v>2026</v>
@@ -14868,7 +14871,7 @@
     </row>
     <row r="707" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="B707">
         <v>2026</v>
@@ -14888,7 +14891,7 @@
     </row>
     <row r="708" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="B708">
         <v>2026</v>
@@ -14908,7 +14911,7 @@
     </row>
     <row r="709" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="B709">
         <v>2026</v>
@@ -14928,7 +14931,7 @@
     </row>
     <row r="710" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="B710">
         <v>2026</v>
@@ -14948,7 +14951,7 @@
     </row>
     <row r="711" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="B711">
         <v>2026</v>
@@ -14968,7 +14971,7 @@
     </row>
     <row r="712" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="B712">
         <v>2026</v>
@@ -14988,7 +14991,7 @@
     </row>
     <row r="713" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="B713">
         <v>2026</v>
@@ -15008,7 +15011,7 @@
     </row>
     <row r="714" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="B714">
         <v>2026</v>
@@ -15028,7 +15031,7 @@
     </row>
     <row r="715" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B715">
         <v>2026</v>
@@ -15048,7 +15051,7 @@
     </row>
     <row r="716" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A716" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B716">
         <v>2026</v>
@@ -15068,7 +15071,7 @@
     </row>
     <row r="717" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B717">
         <v>2026</v>
@@ -15088,7 +15091,7 @@
     </row>
     <row r="718" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B718">
         <v>2026</v>
@@ -15108,7 +15111,7 @@
     </row>
     <row r="719" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="B719">
         <v>2026</v>
@@ -15128,7 +15131,7 @@
     </row>
     <row r="720" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="B720">
         <v>2026</v>
@@ -15148,7 +15151,7 @@
     </row>
     <row r="721" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="B721">
         <v>2026</v>
@@ -15168,7 +15171,7 @@
     </row>
     <row r="722" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="B722">
         <v>2026</v>
@@ -15188,7 +15191,7 @@
     </row>
     <row r="723" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B723">
         <v>2026</v>
@@ -15208,7 +15211,7 @@
     </row>
     <row r="724" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B724">
         <v>2026</v>
@@ -15228,7 +15231,7 @@
     </row>
     <row r="725" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B725">
         <v>2026</v>
@@ -15248,7 +15251,7 @@
     </row>
     <row r="726" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B726">
         <v>2026</v>
@@ -15268,7 +15271,7 @@
     </row>
     <row r="727" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B727">
         <v>2026</v>
@@ -15288,7 +15291,7 @@
     </row>
     <row r="728" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B728">
         <v>2026</v>
@@ -15308,7 +15311,7 @@
     </row>
     <row r="729" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B729">
         <v>2026</v>
@@ -15328,7 +15331,7 @@
     </row>
     <row r="730" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B730">
         <v>2026</v>
@@ -15348,7 +15351,7 @@
     </row>
     <row r="731" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B731">
         <v>2026</v>
@@ -15368,7 +15371,7 @@
     </row>
     <row r="732" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B732">
         <v>2026</v>
@@ -15388,7 +15391,7 @@
     </row>
     <row r="733" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B733">
         <v>2026</v>
@@ -15408,7 +15411,7 @@
     </row>
     <row r="734" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B734">
         <v>2026</v>
@@ -15428,7 +15431,7 @@
     </row>
     <row r="735" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B735">
         <v>2026</v>
@@ -15448,7 +15451,7 @@
     </row>
     <row r="736" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B736">
         <v>2026</v>
@@ -15468,7 +15471,7 @@
     </row>
     <row r="737" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A737" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B737">
         <v>2026</v>
@@ -15488,7 +15491,7 @@
     </row>
     <row r="738" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B738">
         <v>2026</v>
@@ -15508,7 +15511,7 @@
     </row>
     <row r="739" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="B739">
         <v>2026</v>
@@ -15517,10 +15520,10 @@
         <v>93</v>
       </c>
       <c r="D739" s="1">
-        <v>46318</v>
+        <v>46310</v>
       </c>
       <c r="E739" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F739" t="s">
         <v>115</v>
@@ -15528,7 +15531,7 @@
     </row>
     <row r="740" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A740" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="B740">
         <v>2026</v>
@@ -15537,7 +15540,7 @@
         <v>93</v>
       </c>
       <c r="D740" s="1">
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="E740" t="s">
         <v>9</v>
@@ -15548,7 +15551,7 @@
     </row>
     <row r="741" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="B741">
         <v>2026</v>
@@ -15557,7 +15560,7 @@
         <v>93</v>
       </c>
       <c r="D741" s="1">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="E741" t="s">
         <v>9</v>
@@ -15568,7 +15571,7 @@
     </row>
     <row r="742" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="B742">
         <v>2026</v>
@@ -15577,7 +15580,7 @@
         <v>93</v>
       </c>
       <c r="D742" s="1">
-        <v>46346</v>
+        <v>46313</v>
       </c>
       <c r="E742" t="s">
         <v>9</v>
@@ -15588,7 +15591,7 @@
     </row>
     <row r="743" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="B743">
         <v>2026</v>
@@ -15597,10 +15600,10 @@
         <v>93</v>
       </c>
       <c r="D743" s="1">
-        <v>46347</v>
+        <v>46310</v>
       </c>
       <c r="E743" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F743" t="s">
         <v>115</v>
@@ -15608,26 +15611,186 @@
     </row>
     <row r="744" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A744" t="s">
+        <v>117</v>
+      </c>
+      <c r="B744">
+        <v>2026</v>
+      </c>
+      <c r="C744" t="s">
+        <v>93</v>
+      </c>
+      <c r="D744" s="1">
+        <v>46311</v>
+      </c>
+      <c r="E744" t="s">
+        <v>9</v>
+      </c>
+      <c r="F744" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="745" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A745" t="s">
+        <v>117</v>
+      </c>
+      <c r="B745">
+        <v>2026</v>
+      </c>
+      <c r="C745" t="s">
+        <v>93</v>
+      </c>
+      <c r="D745" s="1">
+        <v>46312</v>
+      </c>
+      <c r="E745" t="s">
+        <v>9</v>
+      </c>
+      <c r="F745" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="746" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A746" t="s">
+        <v>117</v>
+      </c>
+      <c r="B746">
+        <v>2026</v>
+      </c>
+      <c r="C746" t="s">
+        <v>93</v>
+      </c>
+      <c r="D746" s="1">
+        <v>46313</v>
+      </c>
+      <c r="E746" t="s">
+        <v>9</v>
+      </c>
+      <c r="F746" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="747" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A747" t="s">
         <v>20</v>
       </c>
-      <c r="B744">
-        <v>2026</v>
-      </c>
-      <c r="C744" t="s">
-        <v>93</v>
-      </c>
-      <c r="D744" s="1">
+      <c r="B747">
+        <v>2026</v>
+      </c>
+      <c r="C747" t="s">
+        <v>93</v>
+      </c>
+      <c r="D747" s="1">
+        <v>46318</v>
+      </c>
+      <c r="E747" t="s">
+        <v>9</v>
+      </c>
+      <c r="F747" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="748" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A748" t="s">
+        <v>20</v>
+      </c>
+      <c r="B748">
+        <v>2026</v>
+      </c>
+      <c r="C748" t="s">
+        <v>93</v>
+      </c>
+      <c r="D748" s="1">
+        <v>46319</v>
+      </c>
+      <c r="E748" t="s">
+        <v>9</v>
+      </c>
+      <c r="F748" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="749" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A749" t="s">
+        <v>20</v>
+      </c>
+      <c r="B749">
+        <v>2026</v>
+      </c>
+      <c r="C749" t="s">
+        <v>93</v>
+      </c>
+      <c r="D749" s="1">
+        <v>46320</v>
+      </c>
+      <c r="E749" t="s">
+        <v>9</v>
+      </c>
+      <c r="F749" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="750" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A750" t="s">
+        <v>20</v>
+      </c>
+      <c r="B750">
+        <v>2026</v>
+      </c>
+      <c r="C750" t="s">
+        <v>93</v>
+      </c>
+      <c r="D750" s="1">
+        <v>46346</v>
+      </c>
+      <c r="E750" t="s">
+        <v>9</v>
+      </c>
+      <c r="F750" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="751" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A751" t="s">
+        <v>20</v>
+      </c>
+      <c r="B751">
+        <v>2026</v>
+      </c>
+      <c r="C751" t="s">
+        <v>93</v>
+      </c>
+      <c r="D751" s="1">
+        <v>46347</v>
+      </c>
+      <c r="E751" t="s">
+        <v>9</v>
+      </c>
+      <c r="F751" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="752" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A752" t="s">
+        <v>20</v>
+      </c>
+      <c r="B752">
+        <v>2026</v>
+      </c>
+      <c r="C752" t="s">
+        <v>93</v>
+      </c>
+      <c r="D752" s="1">
         <v>46348</v>
       </c>
-      <c r="E744" t="s">
-        <v>9</v>
-      </c>
-      <c r="F744" t="s">
+      <c r="E752" t="s">
+        <v>9</v>
+      </c>
+      <c r="F752" t="s">
         <v>115</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F744" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F752" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
